--- a/app/data/quizzes_rows.xlsx
+++ b/app/data/quizzes_rows.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22800" windowHeight="14000"/>
+    <workbookView windowWidth="27360" windowHeight="13040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="500">
   <si>
     <t>quiz</t>
   </si>
@@ -50,7 +50,7 @@
     <t>아이돌</t>
   </si>
   <si>
-    <t xml:space="preserve"> 아이들</t>
+    <t>아이들</t>
   </si>
   <si>
     <t>aitol</t>
@@ -62,7 +62,7 @@
     <t>여름</t>
   </si>
   <si>
-    <t xml:space="preserve"> 어른</t>
+    <t>어른</t>
   </si>
   <si>
     <t>yelum</t>
@@ -74,7 +74,7 @@
     <t>바지</t>
   </si>
   <si>
-    <t xml:space="preserve"> 비자</t>
+    <t>비자</t>
   </si>
   <si>
     <t>paci</t>
@@ -98,7 +98,7 @@
     <t>의자</t>
   </si>
   <si>
-    <t xml:space="preserve"> 의사</t>
+    <t>의사</t>
   </si>
   <si>
     <t>uyca</t>
@@ -134,7 +134,7 @@
     <t>고기</t>
   </si>
   <si>
-    <t xml:space="preserve"> 거기</t>
+    <t>거기</t>
   </si>
   <si>
     <t>koki</t>
@@ -194,7 +194,7 @@
     <t>가을</t>
   </si>
   <si>
-    <t xml:space="preserve"> 가음</t>
+    <t>가음</t>
   </si>
   <si>
     <t>kaul</t>
@@ -206,7 +206,7 @@
     <t>손님</t>
   </si>
   <si>
-    <t xml:space="preserve"> 산님</t>
+    <t>산님</t>
   </si>
   <si>
     <t>sonnim</t>
@@ -218,7 +218,7 @@
     <t>가방</t>
   </si>
   <si>
-    <t xml:space="preserve"> 가랑</t>
+    <t>가랑</t>
   </si>
   <si>
     <t>kapang</t>
@@ -230,7 +230,7 @@
     <t>서울</t>
   </si>
   <si>
-    <t xml:space="preserve"> 서운</t>
+    <t>서운</t>
   </si>
   <si>
     <t>sewul</t>
@@ -242,7 +242,7 @@
     <t>서점</t>
   </si>
   <si>
-    <t xml:space="preserve"> 서섬</t>
+    <t>서섬</t>
   </si>
   <si>
     <t>secem</t>
@@ -290,7 +290,7 @@
     <t>강아지</t>
   </si>
   <si>
-    <t xml:space="preserve"> 장아지</t>
+    <t>장아지</t>
   </si>
   <si>
     <t>kangaci</t>
@@ -302,7 +302,7 @@
     <t>고양이</t>
   </si>
   <si>
-    <t xml:space="preserve"> 고용이</t>
+    <t>고용이</t>
   </si>
   <si>
     <t>koyangi</t>
@@ -314,7 +314,7 @@
     <t>이야기</t>
   </si>
   <si>
-    <t xml:space="preserve"> 이요기</t>
+    <t>이요기</t>
   </si>
   <si>
     <t>iyaki</t>
@@ -326,7 +326,7 @@
     <t>양말</t>
   </si>
   <si>
-    <t xml:space="preserve"> 양볼</t>
+    <t>양볼</t>
   </si>
   <si>
     <t>yangmal</t>
@@ -338,7 +338,7 @@
     <t>아버지</t>
   </si>
   <si>
-    <t xml:space="preserve"> 아버수</t>
+    <t>아버수</t>
   </si>
   <si>
     <t>apeci</t>
@@ -350,7 +350,7 @@
     <t>사람</t>
   </si>
   <si>
-    <t xml:space="preserve"> 사랑</t>
+    <t>사랑</t>
   </si>
   <si>
     <t>salam</t>
@@ -362,7 +362,7 @@
     <t>봄</t>
   </si>
   <si>
-    <t xml:space="preserve"> 본</t>
+    <t>본</t>
   </si>
   <si>
     <t>pom</t>
@@ -374,7 +374,7 @@
     <t>아이</t>
   </si>
   <si>
-    <t xml:space="preserve"> 야이</t>
+    <t>야이</t>
   </si>
   <si>
     <t>ai</t>
@@ -386,7 +386,7 @@
     <t>아시아</t>
   </si>
   <si>
-    <t xml:space="preserve"> 아지야</t>
+    <t>아지야</t>
   </si>
   <si>
     <t>asia</t>
@@ -398,7 +398,7 @@
     <t>수영장</t>
   </si>
   <si>
-    <t xml:space="preserve"> 수영송</t>
+    <t>수영송</t>
   </si>
   <si>
     <t>swuyengcang</t>
@@ -407,7 +407,7 @@
     <t>swuyengsong</t>
   </si>
   <si>
-    <t xml:space="preserve"> 거울</t>
+    <t>거울</t>
   </si>
   <si>
     <t>kewul</t>
@@ -416,7 +416,7 @@
     <t>자기</t>
   </si>
   <si>
-    <t xml:space="preserve"> 저기</t>
+    <t>저기</t>
   </si>
   <si>
     <t>caki</t>
@@ -428,7 +428,7 @@
     <t>의미</t>
   </si>
   <si>
-    <t xml:space="preserve"> 아미</t>
+    <t>아미</t>
   </si>
   <si>
     <t>uymi</t>
@@ -440,7 +440,7 @@
     <t>바람</t>
   </si>
   <si>
-    <t xml:space="preserve"> 바망</t>
+    <t>바망</t>
   </si>
   <si>
     <t>palam</t>
@@ -452,7 +452,7 @@
     <t>유리</t>
   </si>
   <si>
-    <t xml:space="preserve"> 우리</t>
+    <t>우리</t>
   </si>
   <si>
     <t>yuli</t>
@@ -464,7 +464,7 @@
     <t>이름</t>
   </si>
   <si>
-    <t xml:space="preserve"> 이람</t>
+    <t>이람</t>
   </si>
   <si>
     <t>ilum</t>
@@ -476,7 +476,7 @@
     <t>구름</t>
   </si>
   <si>
-    <t xml:space="preserve"> 가름</t>
+    <t>가름</t>
   </si>
   <si>
     <t>kwulum</t>
@@ -488,7 +488,7 @@
     <t>발</t>
   </si>
   <si>
-    <t xml:space="preserve"> 방</t>
+    <t>방</t>
   </si>
   <si>
     <t>pal</t>
@@ -500,7 +500,7 @@
     <t>두부</t>
   </si>
   <si>
-    <t xml:space="preserve"> 두무</t>
+    <t>두무</t>
   </si>
   <si>
     <t>twupwu</t>
@@ -512,7 +512,7 @@
     <t>유명</t>
   </si>
   <si>
-    <t xml:space="preserve"> 유병</t>
+    <t>유병</t>
   </si>
   <si>
     <t>yumyeng</t>
@@ -554,9 +554,6 @@
     <t>오리</t>
   </si>
   <si>
-    <t>우리</t>
-  </si>
-  <si>
     <t>oli</t>
   </si>
   <si>
@@ -1236,9 +1233,6 @@
   </si>
   <si>
     <t>thokki</t>
-  </si>
-  <si>
-    <t>방</t>
   </si>
   <si>
     <t>빵</t>
@@ -1545,19 +1539,13 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1905,27 +1893,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2029,28 +2002,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2059,127 +2035,123 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2563,7 +2535,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultColWidth="7.94117647058824" defaultRowHeight="17.6" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="15.8088235294118" customWidth="1"/>
@@ -3577,10 +3549,10 @@
         <v>174</v>
       </c>
       <c r="C51" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" t="s">
         <v>175</v>
-      </c>
-      <c r="D51" t="s">
-        <v>176</v>
       </c>
       <c r="E51" t="s">
         <v>143</v>
@@ -3594,16 +3566,16 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" t="s">
         <v>177</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>178</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>179</v>
-      </c>
-      <c r="E52" t="s">
-        <v>180</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3614,16 +3586,16 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" t="s">
         <v>181</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>182</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>183</v>
-      </c>
-      <c r="E53" t="s">
-        <v>184</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3634,16 +3606,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" t="s">
         <v>182</v>
-      </c>
-      <c r="C54" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" t="s">
-        <v>184</v>
-      </c>
-      <c r="E54" t="s">
-        <v>183</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -3654,16 +3626,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" t="s">
         <v>185</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>186</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>187</v>
-      </c>
-      <c r="E55" t="s">
-        <v>188</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3674,7 +3646,7 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
         <v>174</v>
@@ -3683,7 +3655,7 @@
         <v>143</v>
       </c>
       <c r="E56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -3703,7 +3675,7 @@
         <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3714,16 +3686,16 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" t="s">
         <v>190</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>191</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>192</v>
-      </c>
-      <c r="E58" t="s">
-        <v>193</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -3734,16 +3706,16 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" t="s">
         <v>194</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>195</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>196</v>
-      </c>
-      <c r="E59" t="s">
-        <v>197</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -3754,16 +3726,16 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" t="s">
         <v>198</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>199</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>200</v>
-      </c>
-      <c r="E60" t="s">
-        <v>201</v>
       </c>
       <c r="F60">
         <v>3</v>
@@ -3774,16 +3746,16 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" t="s">
         <v>202</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>203</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>204</v>
-      </c>
-      <c r="E61" t="s">
-        <v>205</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -3794,16 +3766,16 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
+        <v>205</v>
+      </c>
+      <c r="C62" t="s">
         <v>206</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>207</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>208</v>
-      </c>
-      <c r="E62" t="s">
-        <v>209</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -3814,16 +3786,16 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" t="s">
         <v>210</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>211</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>212</v>
-      </c>
-      <c r="E63" t="s">
-        <v>213</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -3834,16 +3806,16 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" t="s">
         <v>214</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>215</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>216</v>
-      </c>
-      <c r="E64" t="s">
-        <v>217</v>
       </c>
       <c r="F64">
         <v>3</v>
@@ -3854,16 +3826,16 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" t="s">
         <v>218</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>219</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>220</v>
-      </c>
-      <c r="E65" t="s">
-        <v>221</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -3874,16 +3846,16 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" t="s">
         <v>222</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>223</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>224</v>
-      </c>
-      <c r="E66" t="s">
-        <v>225</v>
       </c>
       <c r="F66">
         <v>3</v>
@@ -3894,16 +3866,16 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
+        <v>225</v>
+      </c>
+      <c r="C67" t="s">
         <v>226</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>227</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>228</v>
-      </c>
-      <c r="E67" t="s">
-        <v>229</v>
       </c>
       <c r="F67">
         <v>3</v>
@@ -3914,16 +3886,16 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
+        <v>229</v>
+      </c>
+      <c r="C68" t="s">
         <v>230</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>231</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>232</v>
-      </c>
-      <c r="E68" t="s">
-        <v>233</v>
       </c>
       <c r="F68">
         <v>3</v>
@@ -3934,16 +3906,16 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
+        <v>233</v>
+      </c>
+      <c r="C69" t="s">
         <v>234</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>235</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>236</v>
-      </c>
-      <c r="E69" t="s">
-        <v>237</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -3954,16 +3926,16 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
+        <v>237</v>
+      </c>
+      <c r="C70" t="s">
         <v>238</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>239</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>240</v>
-      </c>
-      <c r="E70" t="s">
-        <v>241</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -3974,16 +3946,16 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71" t="s">
         <v>242</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>243</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>244</v>
-      </c>
-      <c r="E71" t="s">
-        <v>245</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -3994,16 +3966,16 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
+        <v>245</v>
+      </c>
+      <c r="C72" t="s">
         <v>246</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>247</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>248</v>
-      </c>
-      <c r="E72" t="s">
-        <v>249</v>
       </c>
       <c r="F72">
         <v>3</v>
@@ -4014,16 +3986,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C73" t="s">
         <v>250</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>251</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>252</v>
-      </c>
-      <c r="E73" t="s">
-        <v>253</v>
       </c>
       <c r="F73">
         <v>3</v>
@@ -4034,16 +4006,16 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
+        <v>253</v>
+      </c>
+      <c r="C74" t="s">
         <v>254</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>255</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>256</v>
-      </c>
-      <c r="E74" t="s">
-        <v>257</v>
       </c>
       <c r="F74">
         <v>3</v>
@@ -4054,16 +4026,16 @@
         <v>2</v>
       </c>
       <c r="B75" t="s">
+        <v>257</v>
+      </c>
+      <c r="C75" t="s">
         <v>258</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>259</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>260</v>
-      </c>
-      <c r="E75" t="s">
-        <v>261</v>
       </c>
       <c r="F75">
         <v>3</v>
@@ -4074,16 +4046,16 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" t="s">
         <v>262</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>263</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>264</v>
-      </c>
-      <c r="E76" t="s">
-        <v>265</v>
       </c>
       <c r="F76">
         <v>3</v>
@@ -4094,16 +4066,16 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" t="s">
         <v>266</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>267</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>268</v>
-      </c>
-      <c r="E77" t="s">
-        <v>269</v>
       </c>
       <c r="F77">
         <v>3</v>
@@ -4114,16 +4086,16 @@
         <v>3</v>
       </c>
       <c r="B78" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" t="s">
         <v>270</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>271</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>272</v>
-      </c>
-      <c r="E78" t="s">
-        <v>273</v>
       </c>
       <c r="F78">
         <v>3</v>
@@ -4134,16 +4106,16 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
+        <v>273</v>
+      </c>
+      <c r="C79" t="s">
         <v>274</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>275</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>276</v>
-      </c>
-      <c r="E79" t="s">
-        <v>277</v>
       </c>
       <c r="F79">
         <v>3</v>
@@ -4154,16 +4126,16 @@
         <v>3</v>
       </c>
       <c r="B80" t="s">
+        <v>277</v>
+      </c>
+      <c r="C80" t="s">
         <v>278</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>279</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>280</v>
-      </c>
-      <c r="E80" t="s">
-        <v>281</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -4174,16 +4146,16 @@
         <v>3</v>
       </c>
       <c r="B81" t="s">
+        <v>281</v>
+      </c>
+      <c r="C81" t="s">
         <v>282</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>283</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>284</v>
-      </c>
-      <c r="E81" t="s">
-        <v>285</v>
       </c>
       <c r="F81">
         <v>3</v>
@@ -4194,16 +4166,16 @@
         <v>3</v>
       </c>
       <c r="B82" t="s">
+        <v>285</v>
+      </c>
+      <c r="C82" t="s">
         <v>286</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>287</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>288</v>
-      </c>
-      <c r="E82" t="s">
-        <v>289</v>
       </c>
       <c r="F82">
         <v>3</v>
@@ -4214,16 +4186,16 @@
         <v>3</v>
       </c>
       <c r="B83" t="s">
+        <v>289</v>
+      </c>
+      <c r="C83" t="s">
         <v>290</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>291</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>292</v>
-      </c>
-      <c r="E83" t="s">
-        <v>293</v>
       </c>
       <c r="F83">
         <v>3</v>
@@ -4234,16 +4206,16 @@
         <v>3</v>
       </c>
       <c r="B84" t="s">
+        <v>293</v>
+      </c>
+      <c r="C84" t="s">
         <v>294</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>295</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>296</v>
-      </c>
-      <c r="E84" t="s">
-        <v>297</v>
       </c>
       <c r="F84">
         <v>3</v>
@@ -4254,16 +4226,16 @@
         <v>3</v>
       </c>
       <c r="B85" t="s">
+        <v>297</v>
+      </c>
+      <c r="C85" t="s">
         <v>298</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>299</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>300</v>
-      </c>
-      <c r="E85" t="s">
-        <v>301</v>
       </c>
       <c r="F85">
         <v>3</v>
@@ -4274,16 +4246,16 @@
         <v>3</v>
       </c>
       <c r="B86" t="s">
+        <v>301</v>
+      </c>
+      <c r="C86" t="s">
         <v>302</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>303</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>304</v>
-      </c>
-      <c r="E86" t="s">
-        <v>305</v>
       </c>
       <c r="F86">
         <v>3</v>
@@ -4294,16 +4266,16 @@
         <v>3</v>
       </c>
       <c r="B87" t="s">
+        <v>305</v>
+      </c>
+      <c r="C87" t="s">
         <v>306</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>307</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>308</v>
-      </c>
-      <c r="E87" t="s">
-        <v>309</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -4314,16 +4286,16 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
+        <v>309</v>
+      </c>
+      <c r="C88" t="s">
         <v>310</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>311</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>312</v>
-      </c>
-      <c r="E88" t="s">
-        <v>313</v>
       </c>
       <c r="F88">
         <v>3</v>
@@ -4334,16 +4306,16 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
+        <v>313</v>
+      </c>
+      <c r="C89" t="s">
         <v>314</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
+        <v>188</v>
+      </c>
+      <c r="E89" t="s">
         <v>315</v>
-      </c>
-      <c r="D89" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" t="s">
-        <v>316</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -4354,16 +4326,16 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
+        <v>316</v>
+      </c>
+      <c r="C90" t="s">
         <v>317</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>318</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>319</v>
-      </c>
-      <c r="E90" t="s">
-        <v>320</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -4374,16 +4346,16 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
+        <v>320</v>
+      </c>
+      <c r="C91" t="s">
         <v>321</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>322</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>323</v>
-      </c>
-      <c r="E91" t="s">
-        <v>324</v>
       </c>
       <c r="F91">
         <v>3</v>
@@ -4394,16 +4366,16 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
+        <v>324</v>
+      </c>
+      <c r="C92" t="s">
         <v>325</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>326</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>327</v>
-      </c>
-      <c r="E92" t="s">
-        <v>328</v>
       </c>
       <c r="F92">
         <v>3</v>
@@ -4414,16 +4386,16 @@
         <v>4</v>
       </c>
       <c r="B93" t="s">
+        <v>328</v>
+      </c>
+      <c r="C93" t="s">
         <v>329</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>330</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>331</v>
-      </c>
-      <c r="E93" t="s">
-        <v>332</v>
       </c>
       <c r="F93">
         <v>3</v>
@@ -4434,16 +4406,16 @@
         <v>4</v>
       </c>
       <c r="B94" t="s">
+        <v>332</v>
+      </c>
+      <c r="C94" t="s">
         <v>333</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>334</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>335</v>
-      </c>
-      <c r="E94" t="s">
-        <v>336</v>
       </c>
       <c r="F94">
         <v>3</v>
@@ -4454,16 +4426,16 @@
         <v>4</v>
       </c>
       <c r="B95" t="s">
+        <v>336</v>
+      </c>
+      <c r="C95" t="s">
         <v>337</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>338</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>339</v>
-      </c>
-      <c r="E95" t="s">
-        <v>340</v>
       </c>
       <c r="F95">
         <v>3</v>
@@ -4474,16 +4446,16 @@
         <v>4</v>
       </c>
       <c r="B96" t="s">
+        <v>340</v>
+      </c>
+      <c r="C96" t="s">
         <v>341</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>342</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>343</v>
-      </c>
-      <c r="E96" t="s">
-        <v>344</v>
       </c>
       <c r="F96">
         <v>3</v>
@@ -4494,16 +4466,16 @@
         <v>4</v>
       </c>
       <c r="B97" t="s">
+        <v>344</v>
+      </c>
+      <c r="C97" t="s">
         <v>345</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>346</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>347</v>
-      </c>
-      <c r="E97" t="s">
-        <v>348</v>
       </c>
       <c r="F97">
         <v>3</v>
@@ -4514,16 +4486,16 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
+        <v>348</v>
+      </c>
+      <c r="C98" t="s">
         <v>349</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>350</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>351</v>
-      </c>
-      <c r="E98" t="s">
-        <v>352</v>
       </c>
       <c r="F98" s="1">
         <v>4</v>
@@ -4534,16 +4506,16 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
+        <v>352</v>
+      </c>
+      <c r="C99" t="s">
         <v>353</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>354</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>355</v>
-      </c>
-      <c r="E99" t="s">
-        <v>356</v>
       </c>
       <c r="F99" s="1">
         <v>4</v>
@@ -4554,16 +4526,16 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
+        <v>356</v>
+      </c>
+      <c r="C100" t="s">
         <v>357</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>358</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>359</v>
-      </c>
-      <c r="E100" t="s">
-        <v>360</v>
       </c>
       <c r="F100" s="1">
         <v>4</v>
@@ -4574,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
+        <v>360</v>
+      </c>
+      <c r="C101" t="s">
         <v>361</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>362</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>363</v>
-      </c>
-      <c r="E101" t="s">
-        <v>364</v>
       </c>
       <c r="F101" s="1">
         <v>4</v>
@@ -4594,16 +4566,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
+        <v>364</v>
+      </c>
+      <c r="C102" t="s">
         <v>365</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>366</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>367</v>
-      </c>
-      <c r="E102" t="s">
-        <v>368</v>
       </c>
       <c r="F102" s="1">
         <v>4</v>
@@ -4614,13 +4586,13 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C103" t="s">
         <v>39</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E103" t="s">
         <v>41</v>
@@ -4634,16 +4606,16 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C104" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" t="s">
+        <v>319</v>
+      </c>
+      <c r="E104" t="s">
         <v>371</v>
-      </c>
-      <c r="D104" t="s">
-        <v>320</v>
-      </c>
-      <c r="E104" t="s">
-        <v>372</v>
       </c>
       <c r="F104" s="1">
         <v>4</v>
@@ -4657,13 +4629,13 @@
         <v>50</v>
       </c>
       <c r="C105" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D105" t="s">
         <v>52</v>
       </c>
       <c r="E105" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F105" s="1">
         <v>4</v>
@@ -4674,16 +4646,16 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" t="s">
         <v>375</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>376</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>377</v>
-      </c>
-      <c r="E106" t="s">
-        <v>378</v>
       </c>
       <c r="F106" s="1">
         <v>4</v>
@@ -4694,16 +4666,16 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
+        <v>378</v>
+      </c>
+      <c r="C107" t="s">
         <v>379</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>380</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>381</v>
-      </c>
-      <c r="E107" t="s">
-        <v>382</v>
       </c>
       <c r="F107" s="1">
         <v>4</v>
@@ -4714,16 +4686,16 @@
         <v>2</v>
       </c>
       <c r="B108" t="s">
+        <v>382</v>
+      </c>
+      <c r="C108" t="s">
         <v>383</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>384</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>385</v>
-      </c>
-      <c r="E108" t="s">
-        <v>386</v>
       </c>
       <c r="F108" s="1">
         <v>4</v>
@@ -4734,16 +4706,16 @@
         <v>2</v>
       </c>
       <c r="B109" t="s">
+        <v>386</v>
+      </c>
+      <c r="C109" t="s">
         <v>387</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>388</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>389</v>
-      </c>
-      <c r="E109" t="s">
-        <v>390</v>
       </c>
       <c r="F109" s="1">
         <v>4</v>
@@ -4754,16 +4726,16 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
+        <v>390</v>
+      </c>
+      <c r="C110" t="s">
         <v>391</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>392</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>393</v>
-      </c>
-      <c r="E110" t="s">
-        <v>394</v>
       </c>
       <c r="F110" s="1">
         <v>4</v>
@@ -4774,16 +4746,16 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
+        <v>394</v>
+      </c>
+      <c r="C111" t="s">
         <v>395</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>396</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>397</v>
-      </c>
-      <c r="E111" t="s">
-        <v>398</v>
       </c>
       <c r="F111" s="1">
         <v>4</v>
@@ -4794,16 +4766,16 @@
         <v>2</v>
       </c>
       <c r="B112" t="s">
+        <v>398</v>
+      </c>
+      <c r="C112" t="s">
         <v>399</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>400</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>401</v>
-      </c>
-      <c r="E112" t="s">
-        <v>402</v>
       </c>
       <c r="F112" s="1">
         <v>4</v>
@@ -4814,456 +4786,456 @@
         <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>403</v>
+        <v>153</v>
       </c>
       <c r="C113" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D113" t="s">
         <v>155</v>
       </c>
       <c r="E113" t="s">
+        <v>403</v>
+      </c>
+      <c r="F113" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114">
+        <v>2</v>
+      </c>
+      <c r="B114" t="s">
+        <v>404</v>
+      </c>
+      <c r="C114" t="s">
         <v>405</v>
       </c>
-      <c r="F113" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" s="1">
-        <v>2</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>406</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>407</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
+        <v>2</v>
+      </c>
+      <c r="B115" t="s">
         <v>408</v>
       </c>
-      <c r="E114" t="s">
+      <c r="C115" t="s">
         <v>409</v>
       </c>
-      <c r="F114" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" s="1">
-        <v>2</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
         <v>410</v>
       </c>
-      <c r="C115" t="s">
+      <c r="E115" t="s">
         <v>411</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
+        <v>2</v>
+      </c>
+      <c r="B116" t="s">
         <v>412</v>
       </c>
-      <c r="E115" t="s">
+      <c r="C116" t="s">
         <v>413</v>
       </c>
-      <c r="F115" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="1">
-        <v>2</v>
-      </c>
-      <c r="B116" t="s">
+      <c r="D116" t="s">
         <v>414</v>
       </c>
-      <c r="C116" t="s">
+      <c r="E116" t="s">
         <v>415</v>
       </c>
-      <c r="D116" t="s">
+      <c r="F116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117">
+        <v>2</v>
+      </c>
+      <c r="B117" t="s">
         <v>416</v>
       </c>
-      <c r="E116" t="s">
+      <c r="C117" t="s">
         <v>417</v>
       </c>
-      <c r="F116" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" s="1">
-        <v>2</v>
-      </c>
-      <c r="B117" t="s">
+      <c r="D117" t="s">
         <v>418</v>
       </c>
-      <c r="C117" t="s">
+      <c r="E117" t="s">
         <v>419</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118">
+        <v>3</v>
+      </c>
+      <c r="B118" t="s">
         <v>420</v>
       </c>
-      <c r="E117" t="s">
+      <c r="C118" t="s">
         <v>421</v>
       </c>
-      <c r="F117" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" s="1">
-        <v>3</v>
-      </c>
-      <c r="B118" t="s">
+      <c r="D118" t="s">
         <v>422</v>
       </c>
-      <c r="C118" t="s">
+      <c r="E118" t="s">
         <v>423</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119">
+        <v>3</v>
+      </c>
+      <c r="B119" t="s">
         <v>424</v>
       </c>
-      <c r="E118" t="s">
+      <c r="C119" t="s">
         <v>425</v>
       </c>
-      <c r="F118" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" s="1">
-        <v>3</v>
-      </c>
-      <c r="B119" t="s">
+      <c r="D119" t="s">
         <v>426</v>
       </c>
-      <c r="C119" t="s">
+      <c r="E119" t="s">
         <v>427</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120">
+        <v>3</v>
+      </c>
+      <c r="B120" t="s">
         <v>428</v>
       </c>
-      <c r="E119" t="s">
+      <c r="C120" t="s">
         <v>429</v>
       </c>
-      <c r="F119" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" ht="18.35" spans="1:6">
-      <c r="A120" s="1">
-        <v>3</v>
-      </c>
-      <c r="B120" t="s">
+      <c r="D120" t="s">
         <v>430</v>
       </c>
-      <c r="C120" t="s">
+      <c r="E120" t="s">
         <v>431</v>
       </c>
-      <c r="D120" t="s">
+      <c r="F120" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121">
+        <v>3</v>
+      </c>
+      <c r="B121" t="s">
         <v>432</v>
       </c>
-      <c r="E120" t="s">
+      <c r="C121" t="s">
         <v>433</v>
       </c>
-      <c r="F120" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" ht="18.35" spans="1:6">
-      <c r="A121" s="1">
-        <v>3</v>
-      </c>
-      <c r="B121" s="2" t="s">
+      <c r="D121" t="s">
         <v>434</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="E121" t="s">
         <v>435</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122">
+        <v>3</v>
+      </c>
+      <c r="B122" t="s">
         <v>436</v>
       </c>
-      <c r="E121" t="s">
+      <c r="C122" t="s">
         <v>437</v>
       </c>
-      <c r="F121" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" ht="18.35" spans="1:6">
-      <c r="A122" s="1">
-        <v>3</v>
-      </c>
-      <c r="B122" s="2" t="s">
+      <c r="D122" t="s">
         <v>438</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="E122" t="s">
         <v>439</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123">
+        <v>3</v>
+      </c>
+      <c r="B123" t="s">
         <v>440</v>
       </c>
-      <c r="E122" t="s">
+      <c r="C123" t="s">
         <v>441</v>
       </c>
-      <c r="F122" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" ht="18.35" spans="1:6">
-      <c r="A123" s="1">
-        <v>3</v>
-      </c>
-      <c r="B123" s="2" t="s">
+      <c r="D123" t="s">
         <v>442</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="E123" t="s">
         <v>443</v>
       </c>
-      <c r="D123" t="s">
+      <c r="F123" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124">
+        <v>3</v>
+      </c>
+      <c r="B124" t="s">
         <v>444</v>
       </c>
-      <c r="E123" t="s">
+      <c r="C124" t="s">
         <v>445</v>
       </c>
-      <c r="F123" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" s="1">
-        <v>3</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="D124" t="s">
         <v>446</v>
       </c>
-      <c r="C124" t="s">
+      <c r="E124" t="s">
         <v>447</v>
       </c>
-      <c r="D124" t="s">
+      <c r="F124" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125">
+        <v>3</v>
+      </c>
+      <c r="B125" t="s">
         <v>448</v>
       </c>
-      <c r="E124" t="s">
+      <c r="C125" t="s">
         <v>449</v>
       </c>
-      <c r="F124" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" s="1">
-        <v>3</v>
-      </c>
-      <c r="B125" t="s">
+      <c r="D125" t="s">
         <v>450</v>
       </c>
-      <c r="C125" t="s">
+      <c r="E125" t="s">
         <v>451</v>
       </c>
-      <c r="D125" t="s">
+      <c r="F125" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126">
+        <v>3</v>
+      </c>
+      <c r="B126" t="s">
         <v>452</v>
       </c>
-      <c r="E125" t="s">
+      <c r="C126" t="s">
         <v>453</v>
       </c>
-      <c r="F125" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" s="1">
-        <v>3</v>
-      </c>
-      <c r="B126" t="s">
+      <c r="D126" t="s">
         <v>454</v>
       </c>
-      <c r="C126" t="s">
+      <c r="E126" t="s">
         <v>455</v>
       </c>
-      <c r="D126" t="s">
+      <c r="F126" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127">
+        <v>3</v>
+      </c>
+      <c r="B127" t="s">
         <v>456</v>
       </c>
-      <c r="E126" t="s">
+      <c r="C127" t="s">
         <v>457</v>
       </c>
-      <c r="F126" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" s="1">
-        <v>3</v>
-      </c>
-      <c r="B127" t="s">
+      <c r="D127" t="s">
         <v>458</v>
       </c>
-      <c r="C127" t="s">
+      <c r="E127" t="s">
         <v>459</v>
       </c>
-      <c r="D127" t="s">
+      <c r="F127" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
         <v>460</v>
       </c>
-      <c r="E127" t="s">
+      <c r="C128" t="s">
         <v>461</v>
       </c>
-      <c r="F127" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" s="1">
-        <v>4</v>
-      </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
         <v>462</v>
       </c>
-      <c r="C128" t="s">
+      <c r="E128" t="s">
         <v>463</v>
       </c>
-      <c r="D128" t="s">
+      <c r="F128" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" t="s">
         <v>464</v>
       </c>
-      <c r="E128" t="s">
+      <c r="C129" t="s">
         <v>465</v>
       </c>
-      <c r="F128" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" s="1">
-        <v>4</v>
-      </c>
-      <c r="B129" t="s">
+      <c r="D129" t="s">
         <v>466</v>
       </c>
-      <c r="C129" t="s">
+      <c r="E129" t="s">
         <v>467</v>
       </c>
-      <c r="D129" t="s">
+      <c r="F129" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
+        <v>4</v>
+      </c>
+      <c r="B130" t="s">
         <v>468</v>
       </c>
-      <c r="E129" t="s">
+      <c r="C130" t="s">
         <v>469</v>
       </c>
-      <c r="F129" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130" s="1">
-        <v>4</v>
-      </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
         <v>470</v>
       </c>
-      <c r="C130" t="s">
+      <c r="E130" t="s">
         <v>471</v>
       </c>
-      <c r="D130" t="s">
+      <c r="F130" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131">
+        <v>4</v>
+      </c>
+      <c r="B131" t="s">
         <v>472</v>
       </c>
-      <c r="E130" t="s">
+      <c r="C131" t="s">
         <v>473</v>
       </c>
-      <c r="F130" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131" s="1">
-        <v>4</v>
-      </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
         <v>474</v>
       </c>
-      <c r="C131" t="s">
+      <c r="E131" t="s">
         <v>475</v>
       </c>
-      <c r="D131" t="s">
+      <c r="F131" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132">
+        <v>4</v>
+      </c>
+      <c r="B132" t="s">
         <v>476</v>
       </c>
-      <c r="E131" t="s">
+      <c r="C132" t="s">
         <v>477</v>
       </c>
-      <c r="F131" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132" s="1">
-        <v>4</v>
-      </c>
-      <c r="B132" t="s">
+      <c r="D132" t="s">
         <v>478</v>
       </c>
-      <c r="C132" t="s">
+      <c r="E132" t="s">
         <v>479</v>
       </c>
-      <c r="D132" t="s">
+      <c r="F132" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133">
+        <v>4</v>
+      </c>
+      <c r="B133" t="s">
         <v>480</v>
       </c>
-      <c r="E132" t="s">
+      <c r="C133" t="s">
         <v>481</v>
       </c>
-      <c r="F132" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="1">
-        <v>4</v>
-      </c>
-      <c r="B133" t="s">
+      <c r="D133" t="s">
         <v>482</v>
       </c>
-      <c r="C133" t="s">
+      <c r="E133" t="s">
         <v>483</v>
       </c>
-      <c r="D133" t="s">
+      <c r="F133" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134">
+        <v>4</v>
+      </c>
+      <c r="B134" t="s">
         <v>484</v>
       </c>
-      <c r="E133" t="s">
+      <c r="C134" t="s">
         <v>485</v>
       </c>
-      <c r="F133" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="1">
-        <v>4</v>
-      </c>
-      <c r="B134" t="s">
+      <c r="D134" t="s">
         <v>486</v>
       </c>
-      <c r="C134" t="s">
+      <c r="E134" t="s">
         <v>487</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F134" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135">
+        <v>4</v>
+      </c>
+      <c r="B135" t="s">
         <v>488</v>
       </c>
-      <c r="E134" t="s">
+      <c r="C135" t="s">
         <v>489</v>
       </c>
-      <c r="F134" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="1">
-        <v>4</v>
-      </c>
-      <c r="B135" t="s">
+      <c r="D135" t="s">
         <v>490</v>
       </c>
-      <c r="C135" t="s">
+      <c r="E135" t="s">
         <v>491</v>
-      </c>
-      <c r="D135" t="s">
-        <v>492</v>
-      </c>
-      <c r="E135" t="s">
-        <v>493</v>
       </c>
       <c r="F135" s="1">
         <v>4</v>
@@ -5274,49 +5246,679 @@
         <v>4</v>
       </c>
       <c r="B136" t="s">
+        <v>492</v>
+      </c>
+      <c r="C136" t="s">
+        <v>493</v>
+      </c>
+      <c r="D136" t="s">
         <v>494</v>
       </c>
-      <c r="C136" t="s">
+      <c r="E136" t="s">
         <v>495</v>
       </c>
-      <c r="D136" t="s">
+      <c r="F136" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="2">
+        <v>4</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E136" t="s">
+      <c r="C137" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="F136" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" s="1">
-        <v>4</v>
-      </c>
-      <c r="B137" t="s">
+      <c r="D137" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C137" t="s">
+      <c r="E137" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D137" t="s">
-        <v>500</v>
-      </c>
-      <c r="E137" t="s">
-        <v>501</v>
-      </c>
       <c r="F137" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="6:6">
-      <c r="F138" s="1"/>
+    <row r="138" spans="1:6">
+      <c r="A138" s="2">
+        <v>1</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="2">
+        <v>1</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F139" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="2">
+        <v>1</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F140" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="2">
+        <v>1</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F141" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="2">
+        <v>1</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F142" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="2">
+        <v>1</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F143" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="2">
+        <v>1</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F144" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="2">
+        <v>1</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F145" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="2">
+        <v>1</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F146" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="2">
+        <v>1</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F147" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="2">
+        <v>1</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F148" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="2">
+        <v>1</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F149" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="2">
+        <v>1</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F150" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="2">
+        <v>1</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F151" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="2">
+        <v>1</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F152" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="2">
+        <v>1</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F153" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="2">
+        <v>1</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F154" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="2">
+        <v>1</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F155" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="2">
+        <v>1</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F156" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="2">
+        <v>1</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F157" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="2">
+        <v>1</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F158" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="2">
+        <v>1</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F159" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="2">
+        <v>1</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F160" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="2">
+        <v>1</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F161" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="2">
+        <v>1</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F162" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="2">
+        <v>1</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F163" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="2">
+        <v>1</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F164" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="2">
+        <v>1</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F165" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="2">
+        <v>1</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F166" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="2">
+        <v>1</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F167" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="2:5">
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+    </row>
+    <row r="172" spans="2:5">
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F97" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A2:B4 D2:F4 A5:F5 A6:B6 D6:F6 A7:F8 A9:B9 D9:F9 A10:F14 A15:B19 D15:F19 A20:F27 A28:B47 D28:F47 A48:F97" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>